--- a/docs/test-design/codebuddy-test-design-template.xlsx
+++ b/docs/test-design/codebuddy-test-design-template.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试设计总览" sheetId="1" r:id="Rfeb579c8d1574576"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求用户故事拆解" sheetId="2" r:id="Rcdf73bfec6914f41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试场景矩阵" sheetId="3" r:id="Ra173509e40254319"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能测试用例" sheetId="4" r:id="R762e10c6e1884369"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能测试设计" sheetId="5" r:id="Re4f603de8dbf4056"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险与待确认问题" sheetId="6" r:id="R20e70dcbb8ba4f7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自动化建议" sheetId="7" r:id="R63961be21da74392"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试设计总览" sheetId="1" r:id="R9aa33bee0d574f17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求用户故事拆解" sheetId="2" r:id="R18f5be85b0144db7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试场景矩阵" sheetId="3" r:id="R1a4ee64b440c4215"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能测试用例" sheetId="4" r:id="R02a802871df5433f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能测试设计" sheetId="5" r:id="Rb4636ab274a240e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险与待确认问题" sheetId="6" r:id="Rd0ebf766eafd4cf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自动化建议" sheetId="7" r:id="R889d5606f2f34f02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面元素覆盖清单" sheetId="8" r:id="Rb1671cdb3346494e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -36,12 +37,22 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -69,7 +80,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="11">
+  <x:cellXfs count="23">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -93,11 +104,66 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PageElementCoverageTable" displayName="PageElementCoverageTable" ref="A1:O3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="15">
+    <x:tableColumn id="1" name="元素 ID"/>
+    <x:tableColumn id="2" name="Story ID/需求 ID"/>
+    <x:tableColumn id="3" name="页面/入口"/>
+    <x:tableColumn id="4" name="页面 URL/菜单路径"/>
+    <x:tableColumn id="5" name="元素名称/文案"/>
+    <x:tableColumn id="6" name="元素类型"/>
+    <x:tableColumn id="7" name="交互方式"/>
+    <x:tableColumn id="8" name="前置状态/权限"/>
+    <x:tableColumn id="9" name="预期行为"/>
+    <x:tableColumn id="10" name="业务依据/规则来源"/>
+    <x:tableColumn id="11" name="覆盖用例 ID"/>
+    <x:tableColumn id="12" name="覆盖状态"/>
+    <x:tableColumn id="13" name="发现方式"/>
+    <x:tableColumn id="14" name="素材来源"/>
+    <x:tableColumn id="15" name="待确认问题/备注"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1264,4 +1330,209 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="22" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="32" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="32" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="20" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="20" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="34" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="22" t="str">
+        <x:v>元素 ID</x:v>
+      </x:c>
+      <x:c r="B1" s="22" t="str">
+        <x:v>Story ID/需求 ID</x:v>
+      </x:c>
+      <x:c r="C1" s="22" t="str">
+        <x:v>页面/入口</x:v>
+      </x:c>
+      <x:c r="D1" s="22" t="str">
+        <x:v>页面 URL/菜单路径</x:v>
+      </x:c>
+      <x:c r="E1" s="22" t="str">
+        <x:v>元素名称/文案</x:v>
+      </x:c>
+      <x:c r="F1" s="22" t="str">
+        <x:v>元素类型</x:v>
+      </x:c>
+      <x:c r="G1" s="22" t="str">
+        <x:v>交互方式</x:v>
+      </x:c>
+      <x:c r="H1" s="22" t="str">
+        <x:v>前置状态/权限</x:v>
+      </x:c>
+      <x:c r="I1" s="22" t="str">
+        <x:v>预期行为</x:v>
+      </x:c>
+      <x:c r="J1" s="22" t="str">
+        <x:v>业务依据/规则来源</x:v>
+      </x:c>
+      <x:c r="K1" s="22" t="str">
+        <x:v>覆盖用例 ID</x:v>
+      </x:c>
+      <x:c r="L1" s="22" t="str">
+        <x:v>覆盖状态</x:v>
+      </x:c>
+      <x:c r="M1" s="22" t="str">
+        <x:v>发现方式</x:v>
+      </x:c>
+      <x:c r="N1" s="22" t="str">
+        <x:v>素材来源</x:v>
+      </x:c>
+      <x:c r="O1" s="22" t="str">
+        <x:v>待确认问题/备注</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="84" customHeight="1">
+      <x:c r="A2" s="14" t="str">
+        <x:v>EL-LOGIN-001</x:v>
+      </x:c>
+      <x:c r="B2" s="14" t="str">
+        <x:v>STORY-001</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="str">
+        <x:v>登录页</x:v>
+      </x:c>
+      <x:c r="D2" s="14" t="str">
+        <x:v>/login</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="str">
+        <x:v>登录按钮</x:v>
+      </x:c>
+      <x:c r="F2" s="14" t="str">
+        <x:v>按钮</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="str">
+        <x:v>点击</x:v>
+      </x:c>
+      <x:c r="H2" s="14" t="str">
+        <x:v>1. 账号输入框已填写
+2. 密码输入框已填写
+3. 账号状态为启用</x:v>
+      </x:c>
+      <x:c r="I2" s="14" t="str">
+        <x:v>1. 提交登录请求
+2. 登录成功后进入工作台
+3. 登录失败时展示错误提示且不生成会话</x:v>
+      </x:c>
+      <x:c r="J2" s="14" t="str">
+        <x:v>1. 设计文档：登录主流程
+2. 验收标准：正确账号密码登录成功，错误密码登录失败
+3. 页面观察：登录页存在登录按钮</x:v>
+      </x:c>
+      <x:c r="K2" s="14" t="str">
+        <x:v>TC-LOGIN-001; TC-LOGIN-002</x:v>
+      </x:c>
+      <x:c r="L2" s="14" t="str">
+        <x:v>已覆盖</x:v>
+      </x:c>
+      <x:c r="M2" s="14" t="str">
+        <x:v>截图/浏览器实探</x:v>
+      </x:c>
+      <x:c r="N2" s="14" t="str">
+        <x:v>登录页截图、需求文档</x:v>
+      </x:c>
+      <x:c r="O2" s="14" t="str">
+        <x:v>如存在验证码或 MFA，需补充对应元素和用例</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="84" customHeight="1">
+      <x:c r="A3" s="14" t="str">
+        <x:v>EL-LOGIN-002</x:v>
+      </x:c>
+      <x:c r="B3" s="14" t="str">
+        <x:v>STORY-001</x:v>
+      </x:c>
+      <x:c r="C3" s="14" t="str">
+        <x:v>登录页</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="str">
+        <x:v>/login</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="str">
+        <x:v>忘记密码链接</x:v>
+      </x:c>
+      <x:c r="F3" s="14" t="str">
+        <x:v>链接</x:v>
+      </x:c>
+      <x:c r="G3" s="14" t="str">
+        <x:v>点击</x:v>
+      </x:c>
+      <x:c r="H3" s="14" t="str">
+        <x:v>1. 用户位于登录页
+2. 找回密码功能入口可见</x:v>
+      </x:c>
+      <x:c r="I3" s="14" t="str">
+        <x:v>1. 跳转到找回密码页面或打开找回密码流程
+2. 不应改变当前登录态</x:v>
+      </x:c>
+      <x:c r="J3" s="14" t="str">
+        <x:v>1. 页面观察：登录页存在忘记密码链接
+2. 需求文档未描述找回密码业务规则</x:v>
+      </x:c>
+      <x:c r="K3" s="14" t="str">
+        <x:v>待补充</x:v>
+      </x:c>
+      <x:c r="L3" s="14" t="str">
+        <x:v>待确认</x:v>
+      </x:c>
+      <x:c r="M3" s="14" t="str">
+        <x:v>截图</x:v>
+      </x:c>
+      <x:c r="N3" s="14" t="str">
+        <x:v>登录页截图</x:v>
+      </x:c>
+      <x:c r="O3" s="14" t="str">
+        <x:v>需确认本轮需求是否包含找回密码流程</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="8">
+    <x:dataValidation type="list" sqref="F2:F200">
+      <x:formula1>"按钮,链接,菜单,Tab,图标按钮,下拉项,输入框,上传控件,开关,复选框,单选框,表格行操作,批量操作,分页,排序,筛选,弹窗按钮,抽屉按钮,快捷入口,其他"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G2:G200">
+      <x:formula1>"点击,双击,悬停,输入,选择,拖拽,上传,下载,快捷键,其他"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="K2:K200">
+      <x:formula1>"已覆盖,不适用,不测范围,待确认"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="L2:L200">
+      <x:formula1>"需求文档,截图,原型,浏览器实探,computer use,代码/DOM,用户说明"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F2:F200">
+      <x:formula1>"按钮,链接,菜单,Tab,图标按钮,下拉项,输入框,上传控件,开关,复选框,单选框,表格行操作,批量操作,分页,排序,筛选,弹窗按钮,抽屉按钮,快捷入口,其他"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G2:G200">
+      <x:formula1>"点击,双击,悬停,输入,选择,拖拽,上传,下载,快捷键,其他"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="L2:L200">
+      <x:formula1>"已覆盖,不适用,不测范围,待确认"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="M2:M200">
+      <x:formula1>"需求文档,截图,原型,浏览器实探,computer use,代码/DOM,用户说明"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3536a91d48db445e"/>
+  </x:tableParts>
+</x:worksheet>
 </file>
--- a/docs/test-design/codebuddy-test-design-template.xlsx
+++ b/docs/test-design/codebuddy-test-design-template.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试设计总览" sheetId="1" r:id="R9aa33bee0d574f17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求用户故事拆解" sheetId="2" r:id="R18f5be85b0144db7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试场景矩阵" sheetId="3" r:id="R1a4ee64b440c4215"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能测试用例" sheetId="4" r:id="R02a802871df5433f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能测试设计" sheetId="5" r:id="Rb4636ab274a240e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险与待确认问题" sheetId="6" r:id="Rd0ebf766eafd4cf2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自动化建议" sheetId="7" r:id="R889d5606f2f34f02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面元素覆盖清单" sheetId="8" r:id="Rb1671cdb3346494e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试设计总览" sheetId="1" r:id="Rc5fd2a365a8a4ff1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求用户故事拆解" sheetId="2" r:id="Rf0e297674a5d410c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试场景矩阵" sheetId="3" r:id="Rc5df1600e1ca406e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能测试用例" sheetId="4" r:id="R10be33da229c4d54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能测试设计" sheetId="5" r:id="Rf092491958ea4770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险与待确认问题" sheetId="6" r:id="R04182288200349b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自动化建议" sheetId="7" r:id="R6f86c8492d8f4281"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面元素覆盖清单" sheetId="8" r:id="R085c75d6f08f439f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试系统导入用例" sheetId="9" r:id="R7f4564f709074c0d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -37,12 +38,17 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -80,7 +86,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="27">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -134,6 +140,18 @@
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -161,6 +179,40 @@
     <x:tableColumn id="13" name="发现方式"/>
     <x:tableColumn id="14" name="素材来源"/>
     <x:tableColumn id="15" name="待确认问题/备注"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="SystemImportCasesTable" displayName="SystemImportCasesTable" ref="A1:Z2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="26">
+    <x:tableColumn id="1" name="一级模块系统编号"/>
+    <x:tableColumn id="2" name="一级模块名称"/>
+    <x:tableColumn id="3" name="二级模块系统编号"/>
+    <x:tableColumn id="4" name="二级模块名称"/>
+    <x:tableColumn id="5" name="三级模块系统编号"/>
+    <x:tableColumn id="6" name="三级模块名称"/>
+    <x:tableColumn id="7" name="四级模块系统编号"/>
+    <x:tableColumn id="8" name="四级模块名称"/>
+    <x:tableColumn id="9" name="五级模块系统编号"/>
+    <x:tableColumn id="10" name="五级模块名称"/>
+    <x:tableColumn id="11" name="其他模块系统编号"/>
+    <x:tableColumn id="12" name="其他模块名称"/>
+    <x:tableColumn id="13" name="测试用例系统编号"/>
+    <x:tableColumn id="14" name="测试用例序号"/>
+    <x:tableColumn id="15" name="测试用例名称"/>
+    <x:tableColumn id="16" name="测试步骤描述"/>
+    <x:tableColumn id="17" name="测试步骤预期结果"/>
+    <x:tableColumn id="18" name="测试类型"/>
+    <x:tableColumn id="19" name="测试用例级别"/>
+    <x:tableColumn id="20" name="执行方式"/>
+    <x:tableColumn id="21" name="测试用例说明"/>
+    <x:tableColumn id="22" name="前置条件"/>
+    <x:tableColumn id="23" name="维护人"/>
+    <x:tableColumn id="24" name="标签"/>
+    <x:tableColumn id="25" name="备注"/>
+    <x:tableColumn id="26" name="作者"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -1532,7 +1584,203 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3536a91d48db445e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ba2ddd72f0b49a8"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="32" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="42" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="42" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="36" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="36" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="18" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="18" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="18" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="18" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="32" customHeight="1">
+      <x:c r="A1" s="26" t="str">
+        <x:v>一级模块系统编号</x:v>
+      </x:c>
+      <x:c r="B1" s="26" t="str">
+        <x:v>一级模块名称</x:v>
+      </x:c>
+      <x:c r="C1" s="26" t="str">
+        <x:v>二级模块系统编号</x:v>
+      </x:c>
+      <x:c r="D1" s="26" t="str">
+        <x:v>二级模块名称</x:v>
+      </x:c>
+      <x:c r="E1" s="26" t="str">
+        <x:v>三级模块系统编号</x:v>
+      </x:c>
+      <x:c r="F1" s="26" t="str">
+        <x:v>三级模块名称</x:v>
+      </x:c>
+      <x:c r="G1" s="26" t="str">
+        <x:v>四级模块系统编号</x:v>
+      </x:c>
+      <x:c r="H1" s="26" t="str">
+        <x:v>四级模块名称</x:v>
+      </x:c>
+      <x:c r="I1" s="26" t="str">
+        <x:v>五级模块系统编号</x:v>
+      </x:c>
+      <x:c r="J1" s="26" t="str">
+        <x:v>五级模块名称</x:v>
+      </x:c>
+      <x:c r="K1" s="26" t="str">
+        <x:v>其他模块系统编号</x:v>
+      </x:c>
+      <x:c r="L1" s="26" t="str">
+        <x:v>其他模块名称</x:v>
+      </x:c>
+      <x:c r="M1" s="26" t="str">
+        <x:v>测试用例系统编号</x:v>
+      </x:c>
+      <x:c r="N1" s="26" t="str">
+        <x:v>测试用例序号</x:v>
+      </x:c>
+      <x:c r="O1" s="26" t="str">
+        <x:v>测试用例名称</x:v>
+      </x:c>
+      <x:c r="P1" s="26" t="str">
+        <x:v>测试步骤描述</x:v>
+      </x:c>
+      <x:c r="Q1" s="26" t="str">
+        <x:v>测试步骤预期结果</x:v>
+      </x:c>
+      <x:c r="R1" s="26" t="str">
+        <x:v>测试类型</x:v>
+      </x:c>
+      <x:c r="S1" s="26" t="str">
+        <x:v>测试用例级别</x:v>
+      </x:c>
+      <x:c r="T1" s="26" t="str">
+        <x:v>执行方式</x:v>
+      </x:c>
+      <x:c r="U1" s="26" t="str">
+        <x:v>测试用例说明</x:v>
+      </x:c>
+      <x:c r="V1" s="26" t="str">
+        <x:v>前置条件</x:v>
+      </x:c>
+      <x:c r="W1" s="26" t="str">
+        <x:v>维护人</x:v>
+      </x:c>
+      <x:c r="X1" s="26" t="str">
+        <x:v>标签</x:v>
+      </x:c>
+      <x:c r="Y1" s="26" t="str">
+        <x:v>备注</x:v>
+      </x:c>
+      <x:c r="Z1" s="26" t="str">
+        <x:v>作者</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="96" customHeight="1">
+      <x:c r="A2" s="14" t="str"/>
+      <x:c r="B2" s="14" t="str">
+        <x:v>用户管理</x:v>
+      </x:c>
+      <x:c r="C2" s="14" t="str"/>
+      <x:c r="D2" s="14" t="str">
+        <x:v>用户认证</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="str"/>
+      <x:c r="F2" s="14" t="str">
+        <x:v>账号密码登录</x:v>
+      </x:c>
+      <x:c r="G2" s="14" t="str"/>
+      <x:c r="H2" s="14" t="str"/>
+      <x:c r="I2" s="14" t="str"/>
+      <x:c r="J2" s="14" t="str"/>
+      <x:c r="K2" s="14" t="str"/>
+      <x:c r="L2" s="14" t="str"/>
+      <x:c r="M2" s="14" t="str"/>
+      <x:c r="N2" s="14" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="O2" s="14" t="str">
+        <x:v>正确账号密码登录成功</x:v>
+      </x:c>
+      <x:c r="P2" s="14" t="str">
+        <x:v>1. 打开登录页
+2. 输入有效账号和密码
+3. 点击登录按钮</x:v>
+      </x:c>
+      <x:c r="Q2" s="14" t="str">
+        <x:v>1. 登录成功并进入工作台
+2. 页面展示当前用户信息
+3. 系统生成有效会话</x:v>
+      </x:c>
+      <x:c r="R2" s="14" t="str">
+        <x:v>功能测试</x:v>
+      </x:c>
+      <x:c r="S2" s="14" t="str">
+        <x:v>L3</x:v>
+      </x:c>
+      <x:c r="T2" s="14" t="str">
+        <x:v>手工执行</x:v>
+      </x:c>
+      <x:c r="U2" s="14" t="str">
+        <x:v>验证账号密码登录主流程，数据来自功能测试用例 Sheet，可直接粘贴到测试系统导入模板。</x:v>
+      </x:c>
+      <x:c r="V2" s="14" t="str">
+        <x:v>1. 测试环境已部署本次需求版本
+2. 测试账号已准备且状态为启用</x:v>
+      </x:c>
+      <x:c r="W2" s="14" t="str">
+        <x:v>待填写</x:v>
+      </x:c>
+      <x:c r="X2" s="14" t="str">
+        <x:v>用户认证;登录;主流程</x:v>
+      </x:c>
+      <x:c r="Y2" s="14" t="str">
+        <x:v>该 Sheet 为测试系统导入粘贴视图，权威用例仍维护在功能测试用例 Sheet。</x:v>
+      </x:c>
+      <x:c r="Z2" s="14" t="str">
+        <x:v>待填写</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="3">
+    <x:dataValidation type="list" sqref="R2:R500">
+      <x:formula1>"功能测试,性能规格测试,可靠性测试,兼容性测试,可维护性测试,安全性测试,易用性测试"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="S2:S500">
+      <x:formula1>"L1,L2,L3,L4"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="T2:T500">
+      <x:formula1>"手工执行,自动化执行"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf724c60e439d44ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/test-design/codebuddy-test-design-template.xlsx
+++ b/docs/test-design/codebuddy-test-design-template.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试设计总览" sheetId="1" r:id="Rc5fd2a365a8a4ff1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求用户故事拆解" sheetId="2" r:id="Rf0e297674a5d410c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试场景矩阵" sheetId="3" r:id="Rc5df1600e1ca406e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能测试用例" sheetId="4" r:id="R10be33da229c4d54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能测试设计" sheetId="5" r:id="Rf092491958ea4770"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险与待确认问题" sheetId="6" r:id="R04182288200349b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自动化建议" sheetId="7" r:id="R6f86c8492d8f4281"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面元素覆盖清单" sheetId="8" r:id="R085c75d6f08f439f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试系统导入用例" sheetId="9" r:id="R7f4564f709074c0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试设计总览" sheetId="1" r:id="R9dc99240c3924fd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求用户故事拆解" sheetId="2" r:id="R246e5944c6054f45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试场景矩阵" sheetId="3" r:id="R15345b4737f1425d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能测试用例" sheetId="4" r:id="Ra1f4415195f7417d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能测试设计" sheetId="5" r:id="R81be98870cf842e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险与待确认问题" sheetId="6" r:id="R3de2c728796642be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自动化建议" sheetId="7" r:id="Ra2304e22f59141bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面元素覆盖清单" sheetId="8" r:id="R44d17830db64463b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试系统导入用例" sheetId="9" r:id="Rabd7380a912941aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="4">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -37,13 +37,24 @@
       <x:color rgb="FF1F2933"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFC00000"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="7">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E79"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -86,7 +97,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -152,6 +163,12 @@
       <x:alignment horizontal="center" vertical="top" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -1584,7 +1601,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ba2ddd72f0b49a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43e1b31fdf4340b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1664,22 +1681,22 @@
       <x:c r="N1" s="26" t="str">
         <x:v>测试用例序号</x:v>
       </x:c>
-      <x:c r="O1" s="26" t="str">
+      <x:c r="O1" s="28" t="str">
         <x:v>测试用例名称</x:v>
       </x:c>
-      <x:c r="P1" s="26" t="str">
+      <x:c r="P1" s="28" t="str">
         <x:v>测试步骤描述</x:v>
       </x:c>
-      <x:c r="Q1" s="26" t="str">
+      <x:c r="Q1" s="28" t="str">
         <x:v>测试步骤预期结果</x:v>
       </x:c>
-      <x:c r="R1" s="26" t="str">
+      <x:c r="R1" s="28" t="str">
         <x:v>测试类型</x:v>
       </x:c>
-      <x:c r="S1" s="26" t="str">
+      <x:c r="S1" s="28" t="str">
         <x:v>测试用例级别</x:v>
       </x:c>
-      <x:c r="T1" s="26" t="str">
+      <x:c r="T1" s="28" t="str">
         <x:v>执行方式</x:v>
       </x:c>
       <x:c r="U1" s="26" t="str">
@@ -1780,7 +1797,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf724c60e439d44ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b7cceeaeae74e42"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/test-design/codebuddy-test-design-template.xlsx
+++ b/docs/test-design/codebuddy-test-design-template.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试设计总览" sheetId="1" r:id="R9dc99240c3924fd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求用户故事拆解" sheetId="2" r:id="R246e5944c6054f45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试场景矩阵" sheetId="3" r:id="R15345b4737f1425d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能测试用例" sheetId="4" r:id="Ra1f4415195f7417d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能测试设计" sheetId="5" r:id="R81be98870cf842e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险与待确认问题" sheetId="6" r:id="R3de2c728796642be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自动化建议" sheetId="7" r:id="Ra2304e22f59141bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面元素覆盖清单" sheetId="8" r:id="R44d17830db64463b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试系统导入用例" sheetId="9" r:id="Rabd7380a912941aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试设计总览" sheetId="1" r:id="R1fdec800ca584127"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求用户故事拆解" sheetId="2" r:id="R47a4494a4d8a4929"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试场景矩阵" sheetId="3" r:id="R875844d3bcd64fa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="功能测试用例" sheetId="4" r:id="R8f51db00d6c0491c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="性能测试设计" sheetId="5" r:id="Ra61c62b012794d30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险与待确认问题" sheetId="6" r:id="R200d96865b4145ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自动化建议" sheetId="7" r:id="R7a6f11db4d9a4fca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面元素覆盖清单" sheetId="8" r:id="R4fdcbebd660140bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试系统导入用例" sheetId="9" r:id="Rdf90eec89d2f4b61"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1601,7 +1601,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43e1b31fdf4340b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bf11998cbba4a24"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1761,7 +1761,7 @@
         <x:v>L3</x:v>
       </x:c>
       <x:c r="T2" s="14" t="str">
-        <x:v>手工执行</x:v>
+        <x:v>手动</x:v>
       </x:c>
       <x:c r="U2" s="14" t="str">
         <x:v>验证账号密码登录主流程，数据来自功能测试用例 Sheet，可直接粘贴到测试系统导入模板。</x:v>
@@ -1779,25 +1779,23 @@
       <x:c r="Y2" s="14" t="str">
         <x:v>该 Sheet 为测试系统导入粘贴视图，权威用例仍维护在功能测试用例 Sheet。</x:v>
       </x:c>
-      <x:c r="Z2" s="14" t="str">
-        <x:v>待填写</x:v>
-      </x:c>
+      <x:c r="Z2" s="14"/>
     </x:row>
   </x:sheetData>
   <x:dataValidations count="3">
-    <x:dataValidation type="list" sqref="R2:R500">
+    <x:dataValidation type="list" allowBlank="1" sqref="R2:R500">
       <x:formula1>"功能测试,性能规格测试,可靠性测试,兼容性测试,可维护性测试,安全性测试,易用性测试"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="S2:S500">
+    <x:dataValidation type="list" allowBlank="1" sqref="S2:S500">
       <x:formula1>"L1,L2,L3,L4"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="T2:T500">
-      <x:formula1>"手工执行,自动化执行"</x:formula1>
+    <x:dataValidation type="list" allowBlank="1" sqref="T2:T500">
+      <x:formula1>"自动化,手动"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b7cceeaeae74e42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R884dc5a6ec2d4e9b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/test-design/codebuddy-test-design-template.xlsx
+++ b/docs/test-design/codebuddy-test-design-template.xlsx
@@ -12,7 +12,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="自动化建议" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="页面元素覆盖清单" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试设计总览'!$A$1:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'需求用户故事拆解'!$A$1:$J$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'测试场景矩阵'!$A$1:$J$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'功能测试用例'!$A$1:$P$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'性能测试设计'!$A$1:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'风险与待确认问题'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'自动化建议'!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'页面元素覆盖清单'!$A$1:$O$3</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -244,29 +253,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PageElementCoverageTable" displayName="PageElementCoverageTable" ref="A1:O3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <tableColumns count="15">
-    <tableColumn id="1" name="元素 ID"/>
-    <tableColumn id="2" name="Story ID/需求 ID"/>
-    <tableColumn id="3" name="页面/入口"/>
-    <tableColumn id="4" name="页面 URL/菜单路径"/>
-    <tableColumn id="5" name="元素名称/文案"/>
-    <tableColumn id="6" name="元素类型"/>
-    <tableColumn id="7" name="交互方式"/>
-    <tableColumn id="8" name="前置状态/权限"/>
-    <tableColumn id="9" name="预期行为"/>
-    <tableColumn id="10" name="业务依据/规则来源"/>
-    <tableColumn id="11" name="覆盖用例 ID"/>
-    <tableColumn id="12" name="覆盖状态"/>
-    <tableColumn id="13" name="发现方式"/>
-    <tableColumn id="14" name="素材来源"/>
-    <tableColumn id="15" name="待确认问题/备注"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
@@ -628,6 +614,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -768,6 +755,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1002,6 +990,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J4"/>
   <dataValidations count="2">
     <dataValidation sqref="H2:H200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
@@ -1373,6 +1362,7 @@
       <c r="P4" s="9" t="str"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P4"/>
   <dataValidations count="3">
     <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
@@ -1577,6 +1567,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:N2"/>
   <dataValidations count="1">
     <dataValidation sqref="N2:N200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"是,否,待评估"</formula1>
@@ -1732,6 +1723,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H3"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"待确认,处理中,已关闭"</formula1>
@@ -1905,6 +1897,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:I3"/>
   <dataValidations count="1">
     <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
@@ -2181,6 +2174,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O3"/>
   <dataValidations count="8">
     <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"按钮,链接,菜单,Tab,图标按钮,下拉项,输入框,上传控件,开关,复选框,单选框,表格行操作,批量操作,分页,排序,筛选,弹窗按钮,抽屉按钮,快捷入口,其他"</formula1>
@@ -2208,8 +2202,5 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/docs/test-design/codebuddy-test-design-template.xlsx
+++ b/docs/test-design/codebuddy-test-design-template.xlsx
@@ -15,12 +15,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'测试设计总览'!$A$1:$M$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'需求用户故事拆解'!$A$1:$J$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'测试场景矩阵'!$A$1:$J$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'功能测试用例'!$A$1:$P$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'性能测试设计'!$A$1:$N$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'风险与待确认问题'!$A$1:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'测试场景矩阵'!$A$1:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'功能测试用例'!$A$1:$R$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'性能测试设计'!$A$1:$P$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'风险与待确认问题'!$A$1:$J$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'自动化建议'!$A$1:$I$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'页面元素覆盖清单'!$A$1:$O$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'页面元素覆盖清单'!$A$1:$Q$3</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -766,7 +766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="11" min="1" max="1"/>
@@ -779,6 +779,9 @@
     <col width="18" customWidth="1" style="11" min="8" max="8"/>
     <col width="18" customWidth="1" style="11" min="9" max="9"/>
     <col width="34" customWidth="1" style="11" min="10" max="10"/>
+    <col width="34" customWidth="1" style="11" min="11" max="11"/>
+    <col width="34" customWidth="1" style="11" min="12" max="12"/>
+    <col width="34" customWidth="1" style="11" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="11">
@@ -799,35 +802,50 @@
       </c>
       <c r="D1" s="10" t="inlineStr">
         <is>
-          <t>场景类型</t>
+          <t>测试维度</t>
         </is>
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
-          <t>正向/反向</t>
+          <t>DFX维度</t>
         </is>
       </c>
       <c r="F1" s="10" t="inlineStr">
         <is>
-          <t>测试维度</t>
+          <t>DFX场景</t>
         </is>
       </c>
       <c r="G1" s="10" t="inlineStr">
         <is>
+          <t>测试对象/页面元素</t>
+        </is>
+      </c>
+      <c r="H1" s="10" t="inlineStr">
+        <is>
+          <t>输入数据/状态条件</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>观察点</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
           <t>风险等级</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>是否生成用例</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -851,146 +869,59 @@
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>主流程</t>
+          <t>功能测试</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>正向</t>
+          <t>DFT功能</t>
         </is>
       </c>
       <c r="F2" s="9" t="inlineStr">
         <is>
-          <t>核心业务链路</t>
+          <t>正向流程</t>
         </is>
       </c>
       <c r="G2" s="9" t="inlineStr">
         <is>
+          <t>登录按钮、账号输入框、密码输入框</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>启用账号、正确密码</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>登录成功提示、会话生成、进入工作台</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
           <t>高</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
-        <is>
-          <t>覆盖成功登录和会话生成</t>
+      <c r="M2" s="9" t="inlineStr">
+        <is>
+          <t>由 DFX 场景驱动生成对应功能用例</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="72" customHeight="1" s="11">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>SCN-LOGIN-002</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>STORY-001</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>登录失败</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>异常流程</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>反向</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>输入校验</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>高</t>
-        </is>
-      </c>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
-        <is>
-          <t>覆盖密码错误、账号禁用、空输入</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="72" customHeight="1" s="11">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>SCN-LOGIN-003</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="inlineStr">
-        <is>
-          <t>STORY-001</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>登录性能</t>
-        </is>
-      </c>
-      <c r="D4" s="9" t="inlineStr">
-        <is>
-          <t>性能场景</t>
-        </is>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>正向</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>性能/稳定性</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="inlineStr">
-        <is>
-          <t>覆盖高并发登录响应时间</t>
-        </is>
-      </c>
-    </row>
+    <row r="3" ht="72" customHeight="1" s="11"/>
+    <row r="4" ht="72" customHeight="1" s="11"/>
   </sheetData>
-  <autoFilter ref="A1:J4"/>
+  <autoFilter ref="A1:M2"/>
   <dataValidations count="2">
     <dataValidation sqref="H2:H200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
@@ -1009,7 +940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="11" min="1" max="1"/>
@@ -1068,45 +999,55 @@
       </c>
       <c r="H1" s="10" t="inlineStr">
         <is>
+          <t>DFX维度</t>
+        </is>
+      </c>
+      <c r="I1" s="10" t="inlineStr">
+        <is>
+          <t>DFX场景</t>
+        </is>
+      </c>
+      <c r="J1" s="10" t="inlineStr">
+        <is>
           <t>前置条件</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>测试数据</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>操作步骤</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>预期结果</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>实际结果</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>执行状态</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>是否适合自动化</t>
         </is>
       </c>
-      <c r="O1" s="10" t="inlineStr">
+      <c r="Q1" s="10" t="inlineStr">
         <is>
           <t>关联风险</t>
         </is>
       </c>
-      <c r="P1" s="10" t="inlineStr">
+      <c r="R1" s="10" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -1150,18 +1091,28 @@
       </c>
       <c r="H2" s="9" t="inlineStr">
         <is>
+          <t>DFT功能</t>
+        </is>
+      </c>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>正向流程</t>
+        </is>
+      </c>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
           <t>1. 测试环境已部署本次需求版本
 2. 测试账号已准备且状态为启用
 3. 用户已进入目标功能页面</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>1. 账号：&lt;normal_user_account&gt;
 2. 密码：&lt;valid_password&gt;</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>1. 使用有效账号登录系统
 2. 从一级菜单进入用户认证模块，并打开账号密码登录页面
@@ -1169,7 +1120,7 @@
 4. 点击登录按钮</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>1. 系统提交成功并展示成功提示
 2. 页面展示新创建的数据
@@ -1177,23 +1128,23 @@
 4. 操作日志记录本次新增行为</t>
         </is>
       </c>
-      <c r="L2" s="9" t="str"/>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="N2" s="9" t="str"/>
+      <c r="O2" s="9" t="inlineStr">
         <is>
           <t>未执行</t>
         </is>
       </c>
-      <c r="N2" s="9" t="inlineStr">
+      <c r="P2" s="9" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="O2" s="9" t="inlineStr">
+      <c r="Q2" s="9" t="inlineStr">
         <is>
           <t>核心登录链路失败会阻断用户访问</t>
         </is>
       </c>
-      <c r="P2" s="9" t="str"/>
+      <c r="R2" s="9" t="str"/>
     </row>
     <row r="3" ht="72" customHeight="1" s="11">
       <c r="A3" s="9" t="inlineStr">
@@ -1233,18 +1184,28 @@
       </c>
       <c r="H3" s="9" t="inlineStr">
         <is>
+          <t>DFS安全</t>
+        </is>
+      </c>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>权限控制</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
           <t>1. 测试环境已部署本次需求版本
 2. 测试账号已准备且状态为启用
 3. 用户已进入目标功能页面</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>1. 账号：&lt;normal_user_account&gt;
 2. 密码：&lt;invalid_password&gt;</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>1. 打开系统登录入口
 2. 从登录入口进入账号密码登录页面
@@ -1252,31 +1213,31 @@
 4. 点击登录按钮</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>1. 系统拒绝登录
+      <c r="M3" s="9" t="inlineStr">
+        <is>
+          <t>1. 系统提交登录请求并拒绝登录
 2. 页面展示明确但不泄露敏感信息的错误提示
 3. 不生成登录会话
 4. 记录失败日志</t>
         </is>
       </c>
-      <c r="L3" s="9" t="str"/>
-      <c r="M3" s="9" t="inlineStr">
+      <c r="N3" s="9" t="str"/>
+      <c r="O3" s="9" t="inlineStr">
         <is>
           <t>未执行</t>
         </is>
       </c>
-      <c r="N3" s="9" t="inlineStr">
+      <c r="P3" s="9" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="O3" s="9" t="inlineStr">
+      <c r="Q3" s="9" t="inlineStr">
         <is>
           <t>错误提示或登录态生成异常</t>
         </is>
       </c>
-      <c r="P3" s="9" t="str"/>
+      <c r="R3" s="9" t="str"/>
     </row>
     <row r="4" ht="72" customHeight="1" s="11">
       <c r="A4" s="9" t="inlineStr">
@@ -1316,18 +1277,28 @@
       </c>
       <c r="H4" s="9" t="inlineStr">
         <is>
+          <t>DFR可靠</t>
+        </is>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>数据一致</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
           <t>1. 测试环境已部署本次需求版本
 2. 测试账号已准备且状态为启用
 3. 用户已进入目标功能页面</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>1. 账号：&lt;disabled_account&gt;
 2. 密码：&lt;valid_password&gt;</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>1. 打开系统登录入口
 2. 从登录入口进入账号密码登录页面
@@ -1335,34 +1306,34 @@
 4. 点击登录按钮</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>1. 系统拒绝登录
+      <c r="M4" s="9" t="inlineStr">
+        <is>
+          <t>1. 系统提交登录请求并拒绝登录
 2. 页面提示账号不可用或联系管理员
 3. 不生成登录会话
 4. 记录拦截日志</t>
         </is>
       </c>
-      <c r="L4" s="9" t="str"/>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="N4" s="9" t="str"/>
+      <c r="O4" s="9" t="inlineStr">
         <is>
           <t>未执行</t>
         </is>
       </c>
-      <c r="N4" s="9" t="inlineStr">
+      <c r="P4" s="9" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="Q4" s="9" t="inlineStr">
         <is>
           <t>禁用账号绕过风险</t>
         </is>
       </c>
-      <c r="P4" s="9" t="str"/>
+      <c r="R4" s="9" t="str"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P4"/>
+  <autoFilter ref="A1:R4"/>
   <dataValidations count="3">
     <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"P0,P1,P2,P3"</formula1>
@@ -1384,7 +1355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="11" min="1" max="1"/>
@@ -1426,50 +1397,60 @@
       </c>
       <c r="E1" s="10" t="inlineStr">
         <is>
+          <t>DFX维度</t>
+        </is>
+      </c>
+      <c r="F1" s="10" t="inlineStr">
+        <is>
+          <t>DFX场景</t>
+        </is>
+      </c>
+      <c r="G1" s="10" t="inlineStr">
+        <is>
           <t>目标用户量/并发数</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>TPS/QPS 目标</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>响应时间目标</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>数据量级</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="K1" s="10" t="inlineStr">
         <is>
           <t>测试时长</t>
         </is>
       </c>
-      <c r="J1" s="10" t="inlineStr">
+      <c r="L1" s="10" t="inlineStr">
         <is>
           <t>监控指标</t>
         </is>
       </c>
-      <c r="K1" s="10" t="inlineStr">
+      <c r="M1" s="10" t="inlineStr">
         <is>
           <t>通过标准</t>
         </is>
       </c>
-      <c r="L1" s="10" t="inlineStr">
+      <c r="N1" s="10" t="inlineStr">
         <is>
           <t>造数策略</t>
         </is>
       </c>
-      <c r="M1" s="10" t="inlineStr">
+      <c r="O1" s="10" t="inlineStr">
         <is>
           <t>风险说明</t>
         </is>
       </c>
-      <c r="N1" s="10" t="inlineStr">
+      <c r="P1" s="10" t="inlineStr">
         <is>
           <t>是否纳入本轮测试</t>
         </is>
@@ -1498,38 +1479,48 @@
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
+          <t>DFP性能</t>
+        </is>
+      </c>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>响应时间</t>
+        </is>
+      </c>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
           <t>1. 基准：50 并发
 2. 压力：200 并发
 3. 峰值：500 并发</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>1. 基准 QPS &gt;= 100
 2. 压力 QPS &gt;= 300</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>1. P95 &lt;= 800ms
 2. P99 &lt;= 1500ms
 3. 错误率 &lt;= 0.1%</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>1. 用户账号不少于 10,000 条
 2. 活跃测试账号不少于 1,000 条</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>1. 基准测试 10 分钟
 2. 压力测试 30 分钟
 3. 稳定性测试 2 小时</t>
         </is>
       </c>
-      <c r="J2" s="9" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>1. 响应时间
 2. QPS/TPS
@@ -1539,7 +1530,7 @@
 6. 慢查询</t>
         </is>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>1. 达到响应时间目标
 2. 错误率达标
@@ -1547,27 +1538,27 @@
 4. 无登录态异常</t>
         </is>
       </c>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="N2" s="9" t="inlineStr">
         <is>
           <t>1. 批量创建测试账号
 2. 按角色分配账号池
 3. 测试后清理会话和临时数据</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr">
+      <c r="O2" s="9" t="inlineStr">
         <is>
           <t>1. 高并发下认证服务可能成为瓶颈
 2. 日志写入可能影响响应时间</t>
         </is>
       </c>
-      <c r="N2" s="9" t="inlineStr">
+      <c r="P2" s="9" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N2"/>
+  <autoFilter ref="A1:P2"/>
   <dataValidations count="1">
     <dataValidation sqref="N2:N200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"是,否,待评估"</formula1>
@@ -1583,7 +1574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="11" min="1" max="1"/>
@@ -1609,30 +1600,40 @@
       </c>
       <c r="C1" s="10" t="inlineStr">
         <is>
+          <t>关联DFX维度</t>
+        </is>
+      </c>
+      <c r="D1" s="10" t="inlineStr">
+        <is>
+          <t>关联DFX场景</t>
+        </is>
+      </c>
+      <c r="E1" s="10" t="inlineStr">
+        <is>
           <t>描述</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>影响范围</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>风险等级</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>建议处理方式</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="I1" s="10" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="J1" s="10" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
@@ -1651,30 +1652,40 @@
       </c>
       <c r="C2" s="9" t="inlineStr">
         <is>
+          <t>DFS安全</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>权限控制</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
           <t>登录失败策略未明确，可能影响异常用例和安全测试设计。</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>登录模块</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>需求评审中确认错误次数、锁定策略和提示文案。</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>待填写</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
@@ -1693,37 +1704,47 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
+          <t>DFI接口</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>错误码</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
           <t>是否需要验证码或 MFA 校验。</t>
         </is>
       </c>
-      <c r="D3" s="9" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>登录模块</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>向产品和安全负责人确认。</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>待填写</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H3"/>
+  <autoFilter ref="A1:J3"/>
   <dataValidations count="1">
     <dataValidation sqref="H2:H200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"待确认,处理中,已关闭"</formula1>
@@ -1913,7 +1934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" style="11" min="1" max="1"/>
@@ -1971,40 +1992,50 @@
       </c>
       <c r="H1" s="22" t="inlineStr">
         <is>
+          <t>适用DFX维度</t>
+        </is>
+      </c>
+      <c r="I1" s="22" t="inlineStr">
+        <is>
+          <t>适用DFX场景</t>
+        </is>
+      </c>
+      <c r="J1" s="22" t="inlineStr">
+        <is>
           <t>前置状态/权限</t>
         </is>
       </c>
-      <c r="I1" s="22" t="inlineStr">
+      <c r="K1" s="22" t="inlineStr">
         <is>
           <t>预期行为</t>
         </is>
       </c>
-      <c r="J1" s="22" t="inlineStr">
+      <c r="L1" s="22" t="inlineStr">
         <is>
           <t>业务依据/规则来源</t>
         </is>
       </c>
-      <c r="K1" s="22" t="inlineStr">
+      <c r="M1" s="22" t="inlineStr">
         <is>
           <t>覆盖用例 ID</t>
         </is>
       </c>
-      <c r="L1" s="22" t="inlineStr">
+      <c r="N1" s="22" t="inlineStr">
         <is>
           <t>覆盖状态</t>
         </is>
       </c>
-      <c r="M1" s="22" t="inlineStr">
+      <c r="O1" s="22" t="inlineStr">
         <is>
           <t>发现方式</t>
         </is>
       </c>
-      <c r="N1" s="22" t="inlineStr">
+      <c r="P1" s="22" t="inlineStr">
         <is>
           <t>素材来源</t>
         </is>
       </c>
-      <c r="O1" s="22" t="inlineStr">
+      <c r="Q1" s="22" t="inlineStr">
         <is>
           <t>待确认问题/备注</t>
         </is>
@@ -2048,46 +2079,56 @@
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
+          <t>DFT功能;DFU可用</t>
+        </is>
+      </c>
+      <c r="I2" s="14" t="inlineStr">
+        <is>
+          <t>正向流程;操作反馈</t>
+        </is>
+      </c>
+      <c r="J2" s="14" t="inlineStr">
+        <is>
           <t>1. 账号输入框已填写
 2. 密码输入框已填写
 3. 账号状态为启用</t>
         </is>
       </c>
-      <c r="I2" s="14" t="inlineStr">
+      <c r="K2" s="14" t="inlineStr">
         <is>
           <t>1. 提交登录请求
 2. 登录成功后进入工作台
 3. 登录失败时展示错误提示且不生成会话</t>
         </is>
       </c>
-      <c r="J2" s="14" t="inlineStr">
+      <c r="L2" s="14" t="inlineStr">
         <is>
           <t>1. 设计文档：登录主流程
 2. 验收标准：正确账号密码登录成功，错误密码登录失败
 3. 页面观察：登录页存在登录按钮</t>
         </is>
       </c>
-      <c r="K2" s="14" t="inlineStr">
+      <c r="M2" s="14" t="inlineStr">
         <is>
           <t>TC-LOGIN-001; TC-LOGIN-002</t>
         </is>
       </c>
-      <c r="L2" s="14" t="inlineStr">
+      <c r="N2" s="14" t="inlineStr">
         <is>
           <t>已覆盖</t>
         </is>
       </c>
-      <c r="M2" s="14" t="inlineStr">
+      <c r="O2" s="14" t="inlineStr">
         <is>
           <t>截图/浏览器实探</t>
         </is>
       </c>
-      <c r="N2" s="14" t="inlineStr">
+      <c r="P2" s="14" t="inlineStr">
         <is>
           <t>登录页截图、需求文档</t>
         </is>
       </c>
-      <c r="O2" s="14" t="inlineStr">
+      <c r="Q2" s="14" t="inlineStr">
         <is>
           <t>如存在验证码或 MFA，需补充对应元素和用例</t>
         </is>
@@ -2131,50 +2172,60 @@
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
+          <t>DFT功能</t>
+        </is>
+      </c>
+      <c r="I3" s="14" t="inlineStr">
+        <is>
+          <t>异常输入</t>
+        </is>
+      </c>
+      <c r="J3" s="14" t="inlineStr">
+        <is>
           <t>1. 用户位于登录页
 2. 找回密码功能入口可见</t>
         </is>
       </c>
-      <c r="I3" s="14" t="inlineStr">
+      <c r="K3" s="14" t="inlineStr">
         <is>
           <t>1. 跳转到找回密码页面或打开找回密码流程
 2. 不应改变当前登录态</t>
         </is>
       </c>
-      <c r="J3" s="14" t="inlineStr">
+      <c r="L3" s="14" t="inlineStr">
         <is>
           <t>1. 页面观察：登录页存在忘记密码链接
 2. 需求文档未描述找回密码业务规则</t>
         </is>
       </c>
-      <c r="K3" s="14" t="inlineStr">
+      <c r="M3" s="14" t="inlineStr">
         <is>
           <t>待补充</t>
         </is>
       </c>
-      <c r="L3" s="14" t="inlineStr">
+      <c r="N3" s="14" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="M3" s="14" t="inlineStr">
+      <c r="O3" s="14" t="inlineStr">
         <is>
           <t>截图</t>
         </is>
       </c>
-      <c r="N3" s="14" t="inlineStr">
+      <c r="P3" s="14" t="inlineStr">
         <is>
           <t>登录页截图</t>
         </is>
       </c>
-      <c r="O3" s="14" t="inlineStr">
+      <c r="Q3" s="14" t="inlineStr">
         <is>
           <t>需确认本轮需求是否包含找回密码流程</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O3"/>
+  <autoFilter ref="A1:Q3"/>
   <dataValidations count="8">
     <dataValidation sqref="F2:F200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"按钮,链接,菜单,Tab,图标按钮,下拉项,输入框,上传控件,开关,复选框,单选框,表格行操作,批量操作,分页,排序,筛选,弹窗按钮,抽屉按钮,快捷入口,其他"</formula1>

--- a/docs/test-design/codebuddy-test-design-template.xlsx
+++ b/docs/test-design/codebuddy-test-design-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSI\Desktop\code\test_case_gen\docs\test-design\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSI\Desktop\code\AI29\docs\test-design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA6C6574-2DEA-4FBA-B18E-90FDD24562F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73719A0-94EC-4D5B-AB1D-45523B5121DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,8 +19,7 @@
     <sheet name="功能测试用例" sheetId="4" r:id="rId4"/>
     <sheet name="性能测试设计" sheetId="5" r:id="rId5"/>
     <sheet name="风险与待确认问题" sheetId="6" r:id="rId6"/>
-    <sheet name="自动化建议" sheetId="7" r:id="rId7"/>
-    <sheet name="页面元素覆盖清单" sheetId="8" r:id="rId8"/>
+    <sheet name="页面元素覆盖清单" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">测试场景矩阵!$A$1:$M$2</definedName>
@@ -29,15 +28,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">功能测试用例!$A$1:$R$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">性能测试设计!$A$1:$P$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">需求用户故事拆解!$A$1:$J$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">页面元素覆盖清单!$A$1:$Q$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">自动化建议!$A$1:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">页面元素覆盖清单!$A$1:$Q$3</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="198">
   <si>
     <t>项目/模块</t>
   </si>
@@ -565,68 +563,6 @@
   </si>
   <si>
     <t>向产品和安全负责人确认。</t>
-  </si>
-  <si>
-    <t>用例 ID/场景 ID</t>
-  </si>
-  <si>
-    <t>自动化层级</t>
-  </si>
-  <si>
-    <t>自动化价值</t>
-  </si>
-  <si>
-    <t>自动化优先级</t>
-  </si>
-  <si>
-    <t>依赖数据</t>
-  </si>
-  <si>
-    <t>Mock 需求</t>
-  </si>
-  <si>
-    <t>稳定性风险</t>
-  </si>
-  <si>
-    <t>建议框架/工具</t>
-  </si>
-  <si>
-    <t>API/UI/E2E</t>
-  </si>
-  <si>
-    <t>1. 可用账号池
-2. 可重置登录态</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>UI 元素变更可能导致脚本不稳定</t>
-  </si>
-  <si>
-    <t>接口自动化 + 少量 UI 冒烟</t>
-  </si>
-  <si>
-    <t>主链路必须自动化</t>
-  </si>
-  <si>
-    <t>性能测试</t>
-  </si>
-  <si>
-    <t>1. 大量测试账号
-2. 独立压测环境</t>
-  </si>
-  <si>
-    <t>建议 Mock 非核心通知链路</t>
-  </si>
-  <si>
-    <t>共享环境干扰结果</t>
-  </si>
-  <si>
-    <t>JMeter/k6/Locust</t>
-  </si>
-  <si>
-    <t>纳入版本性能基线</t>
   </si>
   <si>
     <t>元素 ID</t>
@@ -1266,9 +1202,10 @@
     <col min="1" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
     <col min="7" max="9" width="18" customWidth="1"/>
-    <col min="10" max="13" width="34" customWidth="1"/>
+    <col min="10" max="10" width="12.5" customWidth="1"/>
+    <col min="11" max="13" width="34" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="30" customHeight="1">
@@ -1388,6 +1325,8 @@
     <col min="14" max="14" width="18" customWidth="1"/>
     <col min="15" max="15" width="34" customWidth="1"/>
     <col min="16" max="16" width="24" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="18" max="18" width="26.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="30" customHeight="1">
@@ -1870,118 +1809,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="34" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="34" customWidth="1"/>
-    <col min="8" max="8" width="28" customWidth="1"/>
-    <col min="9" max="9" width="32" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="72" customHeight="1">
-      <c r="A2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="72" customHeight="1">
-      <c r="A3" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:I3" xr:uid="{00000000-0009-0000-0000-000006000000}"/>
-  <phoneticPr fontId="4" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" sqref="D2:D200" xr:uid="{00000000-0002-0000-0600-000000000000}">
-      <formula1>"P0,P1,P2,P3"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:Q3"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
@@ -1999,161 +1826,161 @@
   <sheetData>
     <row r="1" spans="1:17" ht="27.95" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
       <c r="P1" s="4" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="Q1" s="4" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="84" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="84" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>59</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="N3" s="3" t="s">
         <v>149</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
